--- a/docs/data/jp/xlsx/7309.xlsx
+++ b/docs/data/jp/xlsx/7309.xlsx
@@ -8070,7 +8070,7 @@
     <row r="110">
       <c r="A110" s="18" t="inlineStr">
         <is>
-          <t>Recall Voluntary NOE</t>
+          <t>자발적 리콜 비용</t>
         </is>
       </c>
       <c r="C110" s="20" t="n">
@@ -8323,7 +8323,7 @@
     <row r="115">
       <c r="A115" s="18" t="inlineStr">
         <is>
-          <t>Loss On Free Inspection EL</t>
+          <t>무상 점검 관련 비용</t>
         </is>
       </c>
       <c r="C115" s="20" t="n">
@@ -8361,7 +8361,7 @@
     <row r="117">
       <c r="A117" s="18" t="inlineStr">
         <is>
-          <t>Subsidiary SRestructuring Expense EL</t>
+          <t>자회사 재구축 비용</t>
         </is>
       </c>
       <c r="C117" s="20" t="n">
@@ -8455,7 +8455,7 @@
     <row r="121">
       <c r="A121" s="18" t="inlineStr">
         <is>
-          <t>Loss On Factory Reconstruction EL</t>
+          <t>공장 재건축 관련 비용</t>
         </is>
       </c>
       <c r="C121" s="20" t="n">
@@ -12132,7 +12132,7 @@
     <row r="199">
       <c r="A199" s="18" t="inlineStr">
         <is>
-          <t>Loss On Withdrawal From Business Ope CF</t>
+          <t>사업 철수 손실</t>
         </is>
       </c>
       <c r="O199" s="20" t="n">
@@ -12216,7 +12216,7 @@
     <row r="202">
       <c r="A202" s="18" t="inlineStr">
         <is>
-          <t>Loss On Free Inspection Ope CF</t>
+          <t>무상 점검 관련 비용</t>
         </is>
       </c>
       <c r="C202" s="20" t="n">
@@ -12718,7 +12718,7 @@
     <row r="212">
       <c r="A212" s="18" t="inlineStr">
         <is>
-          <t>Loss On Factory Reconstruction CF</t>
+          <t>공장 재건축 관련 비용</t>
         </is>
       </c>
       <c r="C212" s="20" t="n">
@@ -12764,7 +12764,7 @@
     <row r="213">
       <c r="A213" s="18" t="inlineStr">
         <is>
-          <t>Provision For Loss On Fire Ope CF</t>
+          <t>화재 손실 충당금 증감액</t>
         </is>
       </c>
       <c r="P213" s="20" t="n">
@@ -12805,7 +12805,7 @@
     <row r="215">
       <c r="A215" s="18" t="inlineStr">
         <is>
-          <t>Loss On Factory Reconstruction Ope CF</t>
+          <t>공장 재건축 관련 비용</t>
         </is>
       </c>
       <c r="E215" s="20" t="n">
@@ -12858,7 +12858,7 @@
     <row r="217">
       <c r="A217" s="18" t="inlineStr">
         <is>
-          <t>Subsidiary SRestructuring Expense Ope CF</t>
+          <t>자회사 재구축 비용</t>
         </is>
       </c>
       <c r="C217" s="20" t="n">
@@ -12951,7 +12951,7 @@
     <row r="220">
       <c r="A220" s="18" t="inlineStr">
         <is>
-          <t>Increase Decrease In Accounts Payable Bonuses Ope CF</t>
+          <t>미지급 상여 증감액</t>
         </is>
       </c>
       <c r="E220" s="20" t="n">
@@ -13157,7 +13157,7 @@
     <row r="225">
       <c r="A225" s="18" t="inlineStr">
         <is>
-          <t>Payments For Fire Accident Ope CF</t>
+          <t>화재 관련 지급액</t>
         </is>
       </c>
       <c r="P225" s="20" t="n">
@@ -13179,7 +13179,7 @@
     <row r="226">
       <c r="A226" s="18" t="inlineStr">
         <is>
-          <t>Loss On Free Inspection Paid Ope CF</t>
+          <t>무상 점검 관련 비용 지급액</t>
         </is>
       </c>
       <c r="C226" s="20" t="n">
@@ -13647,7 +13647,7 @@
     <row r="235">
       <c r="A235" s="18" t="inlineStr">
         <is>
-          <t>Payments For Loss On Factory Reconstruction CF</t>
+          <t>공장 재건축 관련 비용 지급액</t>
         </is>
       </c>
       <c r="C235" s="20" t="n">
@@ -13693,7 +13693,7 @@
     <row r="236">
       <c r="A236" s="18" t="inlineStr">
         <is>
-          <t>Payments For Loss On Factory Reconstruction Inv CF</t>
+          <t>공장 재건축 관련 비용 지급액</t>
         </is>
       </c>
       <c r="E236" s="20" t="n">
